--- a/TaylorMorrisonContracts1.xlsx
+++ b/TaylorMorrisonContracts1.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5765,6 +5765,84 @@
         <v>4800</v>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SL Lark Hill - Concrete</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Plan 1</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>13591.5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SL Lark Hill - Concrete</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Plan 2</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>14497.6</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SL Lark Hill - Concrete</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Plan 3</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>17215.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TaylorMorrisonContracts1.xlsx
+++ b/TaylorMorrisonContracts1.xlsx
@@ -418,15 +418,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:G252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +461,11 @@
           <t>Amount</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -486,6 +492,7 @@
       <c r="F2" s="2" t="n">
         <v>23299</v>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,6 +519,7 @@
       <c r="F3" s="2" t="n">
         <v>24258</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,6 +546,7 @@
       <c r="F4" s="2" t="n">
         <v>23116</v>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,6 +573,7 @@
       <c r="F5" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -590,6 +600,7 @@
       <c r="F6" s="2" t="n">
         <v>583</v>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,6 +627,7 @@
       <c r="F7" s="2" t="n">
         <v>425</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -642,6 +654,7 @@
       <c r="F8" s="2" t="n">
         <v>454</v>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -668,6 +681,7 @@
       <c r="F9" s="2" t="n">
         <v>487</v>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -694,6 +708,7 @@
       <c r="F10" s="2" t="n">
         <v>18306</v>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -720,6 +735,7 @@
       <c r="F11" s="2" t="n">
         <v>20643</v>
       </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -746,6 +762,7 @@
       <c r="F12" s="2" t="n">
         <v>21190</v>
       </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -772,6 +789,7 @@
       <c r="F13" s="2" t="n">
         <v>18892</v>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -798,6 +816,7 @@
       <c r="F14" s="2" t="n">
         <v>18565</v>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -824,6 +843,7 @@
       <c r="F15" s="2" t="n">
         <v>18169</v>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -850,6 +870,7 @@
       <c r="F16" s="2" t="n">
         <v>16531</v>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -876,6 +897,7 @@
       <c r="F17" s="2" t="n">
         <v>17737</v>
       </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -902,6 +924,7 @@
       <c r="F18" s="2" t="n">
         <v>2296</v>
       </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +951,7 @@
       <c r="F19" s="2" t="n">
         <v>2206</v>
       </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -954,6 +978,7 @@
       <c r="F20" s="2" t="n">
         <v>2127</v>
       </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -980,6 +1005,7 @@
       <c r="F21" s="2" t="n">
         <v>1362</v>
       </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1006,6 +1032,7 @@
       <c r="F22" s="2" t="n">
         <v>1664</v>
       </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1032,6 +1059,7 @@
       <c r="F23" s="2" t="n">
         <v>494</v>
       </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1058,6 +1086,7 @@
       <c r="F24" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1084,6 +1113,7 @@
       <c r="F25" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1110,6 +1140,7 @@
       <c r="F26" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1136,6 +1167,7 @@
       <c r="F27" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1162,6 +1194,7 @@
       <c r="F28" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1188,6 +1221,7 @@
       <c r="F29" s="2" t="n">
         <v>14017</v>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1214,6 +1248,7 @@
       <c r="F30" s="2" t="n">
         <v>13984</v>
       </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1240,6 +1275,7 @@
       <c r="F31" s="2" t="n">
         <v>14385</v>
       </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1266,6 +1302,7 @@
       <c r="F32" s="2" t="n">
         <v>14626</v>
       </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1292,6 +1329,7 @@
       <c r="F33" s="2" t="n">
         <v>14864</v>
       </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1318,6 +1356,7 @@
       <c r="F34" s="2" t="n">
         <v>1272</v>
       </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1344,6 +1383,7 @@
       <c r="F35" s="2" t="n">
         <v>1263</v>
       </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1370,6 +1410,7 @@
       <c r="F36" s="2" t="n">
         <v>1221</v>
       </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1396,6 +1437,7 @@
       <c r="F37" s="2" t="n">
         <v>1231</v>
       </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1422,6 +1464,7 @@
       <c r="F38" s="2" t="n">
         <v>1246</v>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1448,6 +1491,7 @@
       <c r="F39" s="2" t="n">
         <v>553</v>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1474,6 +1518,7 @@
       <c r="F40" s="2" t="n">
         <v>553</v>
       </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1500,6 +1545,7 @@
       <c r="F41" s="2" t="n">
         <v>491</v>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1526,6 +1572,7 @@
       <c r="F42" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1552,6 +1599,7 @@
       <c r="F43" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1578,6 +1626,7 @@
       <c r="F44" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1604,6 +1653,7 @@
       <c r="F45" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1630,6 +1680,7 @@
       <c r="F46" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1656,6 +1707,7 @@
       <c r="F47" s="2" t="n">
         <v>1015</v>
       </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1682,6 +1734,7 @@
       <c r="F48" s="2" t="n">
         <v>1015</v>
       </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1708,6 +1761,7 @@
       <c r="F49" s="2" t="n">
         <v>1030</v>
       </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1734,6 +1788,7 @@
       <c r="F50" s="2" t="n">
         <v>1015</v>
       </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1760,6 +1815,7 @@
       <c r="F51" s="2" t="n">
         <v>1030</v>
       </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1786,6 +1842,7 @@
       <c r="F52" s="2" t="n">
         <v>26169</v>
       </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1812,6 +1869,7 @@
       <c r="F53" s="2" t="n">
         <v>26637</v>
       </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1838,6 +1896,7 @@
       <c r="F54" s="2" t="n">
         <v>28922</v>
       </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1864,6 +1923,7 @@
       <c r="F55" s="2" t="n">
         <v>30843</v>
       </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1890,6 +1950,7 @@
       <c r="F56" s="2" t="n">
         <v>31391</v>
       </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1916,6 +1977,7 @@
       <c r="F57" s="2" t="n">
         <v>31072</v>
       </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1942,6 +2004,7 @@
       <c r="F58" s="2" t="n">
         <v>33189</v>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1968,6 +2031,7 @@
       <c r="F59" s="2" t="n">
         <v>1344</v>
       </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1994,6 +2058,7 @@
       <c r="F60" s="2" t="n">
         <v>2613</v>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2020,6 +2085,7 @@
       <c r="F61" s="2" t="n">
         <v>3882</v>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2046,6 +2112,7 @@
       <c r="F62" s="2" t="n">
         <v>1544</v>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2072,6 +2139,7 @@
       <c r="F63" s="2" t="n">
         <v>3012</v>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2098,6 +2166,7 @@
       <c r="F64" s="2" t="n">
         <v>4481</v>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2124,6 +2193,7 @@
       <c r="F65" s="2" t="n">
         <v>1743</v>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2150,6 +2220,7 @@
       <c r="F66" s="2" t="n">
         <v>3411</v>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2176,6 +2247,7 @@
       <c r="F67" s="2" t="n">
         <v>5079</v>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2202,6 +2274,7 @@
       <c r="F68" s="2" t="n">
         <v>1640</v>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2228,6 +2301,7 @@
       <c r="F69" s="2" t="n">
         <v>3129</v>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2254,6 +2328,7 @@
       <c r="F70" s="2" t="n">
         <v>4619</v>
       </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2280,6 +2355,7 @@
       <c r="F71" s="2" t="n">
         <v>1806</v>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2306,6 +2382,7 @@
       <c r="F72" s="2" t="n">
         <v>3537</v>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2332,6 +2409,7 @@
       <c r="F73" s="2" t="n">
         <v>5268</v>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2358,6 +2436,7 @@
       <c r="F74" s="2" t="n">
         <v>1313</v>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2384,6 +2463,7 @@
       <c r="F75" s="2" t="n">
         <v>2550</v>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2410,6 +2490,7 @@
       <c r="F76" s="2" t="n">
         <v>3788</v>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2436,6 +2517,7 @@
       <c r="F77" s="2" t="n">
         <v>1670</v>
       </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2462,6 +2544,7 @@
       <c r="F78" s="2" t="n">
         <v>3264</v>
       </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2488,6 +2571,7 @@
       <c r="F79" s="2" t="n">
         <v>4859</v>
       </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2514,6 +2598,7 @@
       <c r="F80" s="2" t="n">
         <v>1069</v>
       </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2540,6 +2625,7 @@
       <c r="F81" s="2" t="n">
         <v>845</v>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2566,6 +2652,7 @@
       <c r="F82" s="2" t="n">
         <v>386</v>
       </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2592,6 +2679,7 @@
       <c r="F83" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2618,6 +2706,7 @@
       <c r="F84" s="2" t="n">
         <v>453</v>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2644,6 +2733,7 @@
       <c r="F85" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2670,6 +2760,7 @@
       <c r="F86" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2696,6 +2787,7 @@
       <c r="F87" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2722,6 +2814,7 @@
       <c r="F88" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2748,6 +2841,7 @@
       <c r="F89" s="2" t="n">
         <v>337</v>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2774,6 +2868,7 @@
       <c r="F90" s="2" t="n">
         <v>375</v>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2800,6 +2895,7 @@
       <c r="F91" s="2" t="n">
         <v>606</v>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2826,6 +2922,7 @@
       <c r="F92" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2852,6 +2949,7 @@
       <c r="F93" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2878,6 +2976,7 @@
       <c r="F94" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2904,6 +3003,7 @@
       <c r="F95" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2930,6 +3030,7 @@
       <c r="F96" s="2" t="n">
         <v>671</v>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2956,6 +3057,7 @@
       <c r="F97" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2982,6 +3084,7 @@
       <c r="F98" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3008,6 +3111,7 @@
       <c r="F99" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3034,6 +3138,7 @@
       <c r="F100" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3060,6 +3165,7 @@
       <c r="F101" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3086,6 +3192,7 @@
       <c r="F102" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3112,6 +3219,7 @@
       <c r="F103" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3138,6 +3246,7 @@
       <c r="F104" s="2" t="n">
         <v>300</v>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3164,6 +3273,7 @@
       <c r="F105" s="2" t="n">
         <v>17619</v>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3190,6 +3300,7 @@
       <c r="F106" s="2" t="n">
         <v>16698</v>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3216,6 +3327,7 @@
       <c r="F107" s="2" t="n">
         <v>15607</v>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3242,6 +3354,7 @@
       <c r="F108" s="2" t="n">
         <v>16364</v>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3268,6 +3381,7 @@
       <c r="F109" s="2" t="n">
         <v>17536</v>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3294,6 +3408,7 @@
       <c r="F110" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3320,6 +3435,7 @@
       <c r="F111" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3346,6 +3462,7 @@
       <c r="F112" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3372,6 +3489,7 @@
       <c r="F113" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3398,6 +3516,7 @@
       <c r="F114" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3424,6 +3543,7 @@
       <c r="F115" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3450,6 +3570,7 @@
       <c r="F116" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3476,6 +3597,7 @@
       <c r="F117" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3502,6 +3624,7 @@
       <c r="F118" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3528,6 +3651,7 @@
       <c r="F119" s="2" t="n">
         <v>250</v>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3554,6 +3678,7 @@
       <c r="F120" s="2" t="n">
         <v>4868.75</v>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3580,6 +3705,7 @@
       <c r="F121" s="2" t="n">
         <v>5421.25</v>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3606,6 +3732,7 @@
       <c r="F122" s="2" t="n">
         <v>4762.75</v>
       </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3632,6 +3759,7 @@
       <c r="F123" s="2" t="n">
         <v>360</v>
       </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3658,6 +3786,7 @@
       <c r="F124" s="2" t="n">
         <v>4646.25</v>
       </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3684,6 +3813,7 @@
       <c r="F125" s="2" t="n">
         <v>5398.75</v>
       </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3710,6 +3840,7 @@
       <c r="F126" s="2" t="n">
         <v>5713.75</v>
       </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3736,6 +3867,7 @@
       <c r="F127" s="2" t="n">
         <v>-2066.75</v>
       </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3762,6 +3894,7 @@
       <c r="F128" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3788,6 +3921,7 @@
       <c r="F129" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3814,6 +3948,7 @@
       <c r="F130" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3840,6 +3975,7 @@
       <c r="F131" s="2" t="n">
         <v>3135.25</v>
       </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3866,6 +4002,7 @@
       <c r="F132" s="2" t="n">
         <v>3240.25</v>
       </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3892,6 +4029,7 @@
       <c r="F133" s="2" t="n">
         <v>3240.25</v>
       </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3918,6 +4056,7 @@
       <c r="F134" s="2" t="n">
         <v>225</v>
       </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3944,6 +4083,7 @@
       <c r="F135" s="2" t="n">
         <v>225</v>
       </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3970,6 +4110,7 @@
       <c r="F136" s="2" t="n">
         <v>225</v>
       </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3996,6 +4137,7 @@
       <c r="F137" s="2" t="n">
         <v>3851.5</v>
       </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4022,6 +4164,7 @@
       <c r="F138" s="2" t="n">
         <v>3718.5</v>
       </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4048,6 +4191,7 @@
       <c r="F139" s="2" t="n">
         <v>3718.5</v>
       </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4074,6 +4218,7 @@
       <c r="F140" s="2" t="n">
         <v>2995.75</v>
       </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4100,6 +4245,7 @@
       <c r="F141" s="2" t="n">
         <v>3901.75</v>
       </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4126,6 +4272,7 @@
       <c r="F142" s="2" t="n">
         <v>3593.75</v>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4152,6 +4299,7 @@
       <c r="F143" s="2" t="n">
         <v>3962</v>
       </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4178,6 +4326,7 @@
       <c r="F144" s="2" t="n">
         <v>3894.25</v>
       </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4204,6 +4353,7 @@
       <c r="F145" s="2" t="n">
         <v>3908.5</v>
       </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4230,6 +4380,7 @@
       <c r="F146" s="2" t="n">
         <v>45</v>
       </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4256,6 +4407,7 @@
       <c r="F147" s="2" t="n">
         <v>45</v>
       </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4282,6 +4434,7 @@
       <c r="F148" s="2" t="n">
         <v>45</v>
       </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4308,6 +4461,7 @@
       <c r="F149" s="2" t="n">
         <v>5036.75</v>
       </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4334,6 +4488,7 @@
       <c r="F150" s="2" t="n">
         <v>5328.75</v>
       </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4360,6 +4515,7 @@
       <c r="F151" s="2" t="n">
         <v>5533.75</v>
       </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4386,6 +4542,7 @@
       <c r="F152" s="2" t="n">
         <v>-204</v>
       </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4412,6 +4569,7 @@
       <c r="F153" s="2" t="n">
         <v>1474</v>
       </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4438,6 +4596,7 @@
       <c r="F154" s="2" t="n">
         <v>-204</v>
       </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4464,6 +4623,7 @@
       <c r="F155" s="2" t="n">
         <v>1213</v>
       </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4490,6 +4650,7 @@
       <c r="F156" s="2" t="n">
         <v>5561.5</v>
       </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4516,6 +4677,7 @@
       <c r="F157" s="2" t="n">
         <v>5759.25</v>
       </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4542,6 +4704,7 @@
       <c r="F158" s="2" t="n">
         <v>4091.5</v>
       </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4568,6 +4731,7 @@
       <c r="F159" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4594,6 +4758,7 @@
       <c r="F160" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4620,6 +4785,7 @@
       <c r="F161" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4646,6 +4812,7 @@
       <c r="F162" s="2" t="n">
         <v>49.5</v>
       </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4672,6 +4839,7 @@
       <c r="F163" s="2" t="n">
         <v>-444.25</v>
       </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4698,6 +4866,7 @@
       <c r="F164" s="2" t="n">
         <v>946</v>
       </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4724,6 +4893,7 @@
       <c r="F165" s="2" t="n">
         <v>4983.85</v>
       </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4750,6 +4920,7 @@
       <c r="F166" s="2" t="n">
         <v>4983.85</v>
       </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4776,6 +4947,7 @@
       <c r="F167" s="2" t="n">
         <v>4983.85</v>
       </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4802,6 +4974,7 @@
       <c r="F168" s="2" t="n">
         <v>965</v>
       </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4828,6 +5001,7 @@
       <c r="F169" s="2" t="n">
         <v>965</v>
       </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4854,6 +5028,7 @@
       <c r="F170" s="2" t="n">
         <v>965</v>
       </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4880,6 +5055,7 @@
       <c r="F171" s="2" t="n">
         <v>5661.53</v>
       </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4906,6 +5082,7 @@
       <c r="F172" s="2" t="n">
         <v>5661.53</v>
       </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4932,6 +5109,7 @@
       <c r="F173" s="2" t="n">
         <v>5661.53</v>
       </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4958,6 +5136,7 @@
       <c r="F174" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4984,6 +5163,7 @@
       <c r="F175" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5010,6 +5190,7 @@
       <c r="F176" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5036,6 +5217,7 @@
       <c r="F177" s="2" t="n">
         <v>4458.74</v>
       </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5062,6 +5244,7 @@
       <c r="F178" s="2" t="n">
         <v>4769.37</v>
       </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5088,6 +5271,7 @@
       <c r="F179" s="2" t="n">
         <v>4673.79</v>
       </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5114,6 +5298,7 @@
       <c r="F180" s="2" t="n">
         <v>-71.69</v>
       </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5140,6 +5325,7 @@
       <c r="F181" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5166,6 +5352,7 @@
       <c r="F182" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5192,6 +5379,7 @@
       <c r="F183" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5218,6 +5406,7 @@
       <c r="F184" s="2" t="n">
         <v>4856.21</v>
       </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5244,6 +5433,7 @@
       <c r="F185" s="2" t="n">
         <v>4832.31</v>
       </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5270,6 +5460,7 @@
       <c r="F186" s="2" t="n">
         <v>4426.11</v>
       </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5296,6 +5487,7 @@
       <c r="F187" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5322,6 +5514,7 @@
       <c r="F188" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5348,6 +5541,7 @@
       <c r="F189" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5374,6 +5568,7 @@
       <c r="F190" s="2" t="n">
         <v>3053.74</v>
       </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5400,6 +5595,7 @@
       <c r="F191" s="2" t="n">
         <v>3149.31</v>
       </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5426,6 +5622,7 @@
       <c r="F192" s="2" t="n">
         <v>4907.96</v>
       </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5452,6 +5649,7 @@
       <c r="F193" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5478,6 +5676,7 @@
       <c r="F194" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5504,6 +5703,7 @@
       <c r="F195" s="2" t="n">
         <v>49.88</v>
       </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5530,6 +5730,7 @@
       <c r="F196" s="2" t="n">
         <v>4688.35</v>
       </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5556,6 +5757,7 @@
       <c r="F197" s="2" t="n">
         <v>4688.35</v>
       </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5582,6 +5784,7 @@
       <c r="F198" s="2" t="n">
         <v>4688.35</v>
       </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5608,6 +5811,7 @@
       <c r="F199" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5634,6 +5838,7 @@
       <c r="F200" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5660,6 +5865,7 @@
       <c r="F201" s="2" t="n">
         <v>450</v>
       </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5686,6 +5892,7 @@
       <c r="F202" s="2" t="n">
         <v>4800</v>
       </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5712,6 +5919,7 @@
       <c r="F203" s="2" t="n">
         <v>4800</v>
       </c>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5738,6 +5946,7 @@
       <c r="F204" s="2" t="n">
         <v>4800</v>
       </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5764,6 +5973,7 @@
       <c r="F205" s="2" t="n">
         <v>4800</v>
       </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5790,6 +6000,7 @@
       <c r="F206" s="2" t="n">
         <v>13591.5</v>
       </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5816,6 +6027,7 @@
       <c r="F207" s="2" t="n">
         <v>14497.6</v>
       </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5841,6 +6053,1371 @@
       </c>
       <c r="F208" s="2" t="n">
         <v>17215.9</v>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>C301A1569 - Plan 1/1X - Tiki</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>18043</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>C301A1763 - Plan 2 - Zinnia</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>20347</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>C301A1822 - Plan 2X - ZinniaX</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>20885</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Plan 1 - Amaryllis</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>4983.85</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Plan 2 - Calla Lily</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>4983.85</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Plan 3 - Daphne</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="n">
+        <v>4983.85</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Plan 1 - Amaryllis</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Plan 2 - Calla Lily</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Plan 3 - Daphne</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Plan 1 - Amaryllis</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="n">
+        <v>3007.92</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Plan 2 - Calla Lily</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="n">
+        <v>3102.06</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Plan 3 - Daphne</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="n">
+        <v>4834.32</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Plan 1 - Amaryllis</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Plan 2 - Calla Lily</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>LLV Portofino 40s</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Plan 3 - Daphne</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Plan 2 - Sunflower</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>4783.35</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Plan 3 - Tulip</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="n">
+        <v>4759.8</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Plan 4 - Violet</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="n">
+        <v>4359.7</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Plan 2 - Sunflower</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Plan 3 - Tulip</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Plan 4 - Violet</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Plan 2 - Sunflower</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="n">
+        <v>4688.35</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Plan 3 - Tulip</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>4688.35</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Plan 4 - Violet</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="n">
+        <v>4688.35</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Plan 2 - Sunflower</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Plan 3 - Tulip</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>LLV Portofino 50s</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Plan 4 - Violet</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Plan 1 - Allium</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>5661.53</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Plan 2 - Lotus</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="n">
+        <v>5661.53</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Plan 3 - Peony</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>5661.53</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Plan 1 - Allium</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Plan 2 - Lotus</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Plan 3 - Peony</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additi…</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Plan 1 - Allium</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="n">
+        <v>4391.84</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Plan 2 - Lotus</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="n">
+        <v>4697.81</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Plan 3 - Peony</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Pavers</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="n">
+        <v>4603.67</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Plan 2 - Lotus</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>PVO-OC1ELVMB B Elevation</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="n">
+        <v>-71.69</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Plan 1 - Allium</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Plan 2 - Lotus</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>LLV Portofino 60s</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Plan 3 - Peony</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>PVO-OC1ESDRGAR Garage Service Door</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>MFLLC 40s (Mountain Falls)</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Plan 1</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="n">
+        <v>4755</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>MFLLC 40s (Mountain Falls)</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Plan 2</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="n">
+        <v>4755</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>MFLLC 40s (Mountain Falls)</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Plan 3</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="n">
+        <v>4755</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>MFLLC 40s (Mountain Falls)</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Plan 4</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>4755</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/TaylorMorrisonContracts1.xlsx
+++ b/TaylorMorrisonContracts1.xlsx
@@ -418,16 +418,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G252"/>
+  <dimension ref="A1:G255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6066,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46220</v>
+        <v>46174</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46220</v>
+        <v>46174</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46220</v>
+        <v>46174</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -7415,6 +7415,99 @@
         <v>4755</v>
       </c>
       <c r="G252" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>C301A1569 - Plan 1/1X - Tiki</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>FND-WHITESHEET01 Dropped Garage</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>C301A1763 - Plan 2 - Zinnia</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>FND-WHITESHEET01 Dropped Garage</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Esplanade Duplex - Concrete</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>C301A1822 - Plan 2X - ZinniaX</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>FND-WHITESHEET01 Dropped Garage</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="G255" t="inlineStr">
         <is>
           <t>Price reduced from contract approved by Tony</t>
         </is>

--- a/TaylorMorrisonContracts1.xlsx
+++ b/TaylorMorrisonContracts1.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,10 +48,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G255"/>
+  <dimension ref="A1:G325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,7 +492,6 @@
       <c r="F2" s="2" t="n">
         <v>23299</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,7 +502,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -519,7 +518,6 @@
       <c r="F3" s="2" t="n">
         <v>24258</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,7 +528,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -546,7 +544,6 @@
       <c r="F4" s="2" t="n">
         <v>23116</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -557,7 +554,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -573,7 +570,6 @@
       <c r="F5" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -584,7 +580,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -600,7 +596,6 @@
       <c r="F6" s="2" t="n">
         <v>583</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -611,7 +606,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -627,7 +622,6 @@
       <c r="F7" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -638,7 +632,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -654,7 +648,6 @@
       <c r="F8" s="2" t="n">
         <v>454</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -665,7 +658,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -681,7 +674,6 @@
       <c r="F9" s="2" t="n">
         <v>487</v>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,7 +684,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -708,7 +700,6 @@
       <c r="F10" s="2" t="n">
         <v>18306</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -719,7 +710,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -735,7 +726,6 @@
       <c r="F11" s="2" t="n">
         <v>20643</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -746,7 +736,7 @@
       <c r="B12" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,7 +752,6 @@
       <c r="F12" s="2" t="n">
         <v>21190</v>
       </c>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +762,7 @@
       <c r="B13" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -789,7 +778,6 @@
       <c r="F13" s="2" t="n">
         <v>18892</v>
       </c>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -800,7 +788,7 @@
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,7 +804,6 @@
       <c r="F14" s="2" t="n">
         <v>18565</v>
       </c>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -827,7 +814,7 @@
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -843,7 +830,6 @@
       <c r="F15" s="2" t="n">
         <v>18169</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -854,7 +840,7 @@
       <c r="B16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -870,7 +856,6 @@
       <c r="F16" s="2" t="n">
         <v>16531</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -881,7 +866,7 @@
       <c r="B17" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -897,7 +882,6 @@
       <c r="F17" s="2" t="n">
         <v>17737</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -908,7 +892,7 @@
       <c r="B18" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -924,7 +908,6 @@
       <c r="F18" s="2" t="n">
         <v>2296</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -935,7 +918,7 @@
       <c r="B19" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -951,7 +934,6 @@
       <c r="F19" s="2" t="n">
         <v>2206</v>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -962,7 +944,7 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -978,7 +960,6 @@
       <c r="F20" s="2" t="n">
         <v>2127</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -989,7 +970,7 @@
       <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1005,7 +986,6 @@
       <c r="F21" s="2" t="n">
         <v>1362</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1016,7 +996,7 @@
       <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1032,7 +1012,6 @@
       <c r="F22" s="2" t="n">
         <v>1664</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1043,7 +1022,7 @@
       <c r="B23" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1059,7 +1038,6 @@
       <c r="F23" s="2" t="n">
         <v>494</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1070,7 +1048,7 @@
       <c r="B24" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1086,7 +1064,6 @@
       <c r="F24" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1097,7 +1074,7 @@
       <c r="B25" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1113,7 +1090,6 @@
       <c r="F25" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1124,7 +1100,7 @@
       <c r="B26" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1140,7 +1116,6 @@
       <c r="F26" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1151,7 +1126,7 @@
       <c r="B27" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1167,7 +1142,6 @@
       <c r="F27" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1178,7 +1152,7 @@
       <c r="B28" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1194,7 +1168,6 @@
       <c r="F28" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1205,7 +1178,7 @@
       <c r="B29" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1221,7 +1194,6 @@
       <c r="F29" s="2" t="n">
         <v>14017</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1232,7 +1204,7 @@
       <c r="B30" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1248,7 +1220,6 @@
       <c r="F30" s="2" t="n">
         <v>13984</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1259,7 +1230,7 @@
       <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1275,7 +1246,6 @@
       <c r="F31" s="2" t="n">
         <v>14385</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1286,7 +1256,7 @@
       <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -1302,7 +1272,6 @@
       <c r="F32" s="2" t="n">
         <v>14626</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1313,7 +1282,7 @@
       <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -1329,7 +1298,6 @@
       <c r="F33" s="2" t="n">
         <v>14864</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1340,7 +1308,7 @@
       <c r="B34" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -1356,7 +1324,6 @@
       <c r="F34" s="2" t="n">
         <v>1272</v>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1367,7 +1334,7 @@
       <c r="B35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -1383,7 +1350,6 @@
       <c r="F35" s="2" t="n">
         <v>1263</v>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1394,7 +1360,7 @@
       <c r="B36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -1410,7 +1376,6 @@
       <c r="F36" s="2" t="n">
         <v>1221</v>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1421,7 +1386,7 @@
       <c r="B37" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -1437,7 +1402,6 @@
       <c r="F37" s="2" t="n">
         <v>1231</v>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1448,7 +1412,7 @@
       <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -1464,7 +1428,6 @@
       <c r="F38" s="2" t="n">
         <v>1246</v>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1475,7 +1438,7 @@
       <c r="B39" t="n">
         <v>1</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -1491,7 +1454,6 @@
       <c r="F39" s="2" t="n">
         <v>553</v>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1502,7 +1464,7 @@
       <c r="B40" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -1518,7 +1480,6 @@
       <c r="F40" s="2" t="n">
         <v>553</v>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1529,7 +1490,7 @@
       <c r="B41" t="n">
         <v>1</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -1545,7 +1506,6 @@
       <c r="F41" s="2" t="n">
         <v>491</v>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1556,7 +1516,7 @@
       <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -1572,7 +1532,6 @@
       <c r="F42" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1583,7 +1542,7 @@
       <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -1599,7 +1558,6 @@
       <c r="F43" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1610,7 +1568,7 @@
       <c r="B44" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -1626,7 +1584,6 @@
       <c r="F44" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1637,7 +1594,7 @@
       <c r="B45" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -1653,7 +1610,6 @@
       <c r="F45" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1664,7 +1620,7 @@
       <c r="B46" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -1680,7 +1636,6 @@
       <c r="F46" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1691,7 +1646,7 @@
       <c r="B47" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -1707,7 +1662,6 @@
       <c r="F47" s="2" t="n">
         <v>1015</v>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1718,7 +1672,7 @@
       <c r="B48" t="n">
         <v>1</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -1734,7 +1688,6 @@
       <c r="F48" s="2" t="n">
         <v>1015</v>
       </c>
-      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1745,7 +1698,7 @@
       <c r="B49" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -1761,7 +1714,6 @@
       <c r="F49" s="2" t="n">
         <v>1030</v>
       </c>
-      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1772,7 +1724,7 @@
       <c r="B50" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -1788,7 +1740,6 @@
       <c r="F50" s="2" t="n">
         <v>1015</v>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1799,7 +1750,7 @@
       <c r="B51" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -1815,7 +1766,6 @@
       <c r="F51" s="2" t="n">
         <v>1030</v>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1826,7 +1776,7 @@
       <c r="B52" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -1842,7 +1792,6 @@
       <c r="F52" s="2" t="n">
         <v>26169</v>
       </c>
-      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1853,7 +1802,7 @@
       <c r="B53" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -1869,7 +1818,6 @@
       <c r="F53" s="2" t="n">
         <v>26637</v>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1880,7 +1828,7 @@
       <c r="B54" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -1896,7 +1844,6 @@
       <c r="F54" s="2" t="n">
         <v>28922</v>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1907,7 +1854,7 @@
       <c r="B55" t="n">
         <v>1</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -1923,7 +1870,6 @@
       <c r="F55" s="2" t="n">
         <v>30843</v>
       </c>
-      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1934,7 +1880,7 @@
       <c r="B56" t="n">
         <v>1</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -1950,7 +1896,6 @@
       <c r="F56" s="2" t="n">
         <v>31391</v>
       </c>
-      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1961,7 +1906,7 @@
       <c r="B57" t="n">
         <v>1</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -1977,7 +1922,6 @@
       <c r="F57" s="2" t="n">
         <v>31072</v>
       </c>
-      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1988,7 +1932,7 @@
       <c r="B58" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -2004,7 +1948,6 @@
       <c r="F58" s="2" t="n">
         <v>33189</v>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2015,7 +1958,7 @@
       <c r="B59" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -2031,7 +1974,6 @@
       <c r="F59" s="2" t="n">
         <v>1344</v>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2042,7 +1984,7 @@
       <c r="B60" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -2058,7 +2000,6 @@
       <c r="F60" s="2" t="n">
         <v>2613</v>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2069,7 +2010,7 @@
       <c r="B61" t="n">
         <v>1</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -2085,7 +2026,6 @@
       <c r="F61" s="2" t="n">
         <v>3882</v>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2096,7 +2036,7 @@
       <c r="B62" t="n">
         <v>1</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -2112,7 +2052,6 @@
       <c r="F62" s="2" t="n">
         <v>1544</v>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2123,7 +2062,7 @@
       <c r="B63" t="n">
         <v>1</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -2139,7 +2078,6 @@
       <c r="F63" s="2" t="n">
         <v>3012</v>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2150,7 +2088,7 @@
       <c r="B64" t="n">
         <v>1</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -2166,7 +2104,6 @@
       <c r="F64" s="2" t="n">
         <v>4481</v>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2177,7 +2114,7 @@
       <c r="B65" t="n">
         <v>1</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -2193,7 +2130,6 @@
       <c r="F65" s="2" t="n">
         <v>1743</v>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2204,7 +2140,7 @@
       <c r="B66" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -2220,7 +2156,6 @@
       <c r="F66" s="2" t="n">
         <v>3411</v>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2231,7 +2166,7 @@
       <c r="B67" t="n">
         <v>1</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -2247,7 +2182,6 @@
       <c r="F67" s="2" t="n">
         <v>5079</v>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2258,7 +2192,7 @@
       <c r="B68" t="n">
         <v>1</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -2274,7 +2208,6 @@
       <c r="F68" s="2" t="n">
         <v>1640</v>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2285,7 +2218,7 @@
       <c r="B69" t="n">
         <v>1</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -2301,7 +2234,6 @@
       <c r="F69" s="2" t="n">
         <v>3129</v>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2312,7 +2244,7 @@
       <c r="B70" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -2328,7 +2260,6 @@
       <c r="F70" s="2" t="n">
         <v>4619</v>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2339,7 +2270,7 @@
       <c r="B71" t="n">
         <v>1</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -2355,7 +2286,6 @@
       <c r="F71" s="2" t="n">
         <v>1806</v>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2366,7 +2296,7 @@
       <c r="B72" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -2382,7 +2312,6 @@
       <c r="F72" s="2" t="n">
         <v>3537</v>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2393,7 +2322,7 @@
       <c r="B73" t="n">
         <v>1</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -2409,7 +2338,6 @@
       <c r="F73" s="2" t="n">
         <v>5268</v>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2420,7 +2348,7 @@
       <c r="B74" t="n">
         <v>1</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -2436,7 +2364,6 @@
       <c r="F74" s="2" t="n">
         <v>1313</v>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2447,7 +2374,7 @@
       <c r="B75" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -2463,7 +2390,6 @@
       <c r="F75" s="2" t="n">
         <v>2550</v>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2474,7 +2400,7 @@
       <c r="B76" t="n">
         <v>1</v>
       </c>
-      <c r="C76" s="1" t="n">
+      <c r="C76" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -2490,7 +2416,6 @@
       <c r="F76" s="2" t="n">
         <v>3788</v>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2501,7 +2426,7 @@
       <c r="B77" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C77" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -2517,7 +2442,6 @@
       <c r="F77" s="2" t="n">
         <v>1670</v>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2528,7 +2452,7 @@
       <c r="B78" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="1" t="n">
+      <c r="C78" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -2544,7 +2468,6 @@
       <c r="F78" s="2" t="n">
         <v>3264</v>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2555,7 +2478,7 @@
       <c r="B79" t="n">
         <v>1</v>
       </c>
-      <c r="C79" s="1" t="n">
+      <c r="C79" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -2571,7 +2494,6 @@
       <c r="F79" s="2" t="n">
         <v>4859</v>
       </c>
-      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2582,7 +2504,7 @@
       <c r="B80" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="1" t="n">
+      <c r="C80" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -2598,7 +2520,6 @@
       <c r="F80" s="2" t="n">
         <v>1069</v>
       </c>
-      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2609,7 +2530,7 @@
       <c r="B81" t="n">
         <v>1</v>
       </c>
-      <c r="C81" s="1" t="n">
+      <c r="C81" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -2625,7 +2546,6 @@
       <c r="F81" s="2" t="n">
         <v>845</v>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2636,7 +2556,7 @@
       <c r="B82" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C82" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -2652,7 +2572,6 @@
       <c r="F82" s="2" t="n">
         <v>386</v>
       </c>
-      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2663,7 +2582,7 @@
       <c r="B83" t="n">
         <v>1</v>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C83" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -2679,7 +2598,6 @@
       <c r="F83" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2690,7 +2608,7 @@
       <c r="B84" t="n">
         <v>1</v>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C84" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -2706,7 +2624,6 @@
       <c r="F84" s="2" t="n">
         <v>453</v>
       </c>
-      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2717,7 +2634,7 @@
       <c r="B85" t="n">
         <v>1</v>
       </c>
-      <c r="C85" s="1" t="n">
+      <c r="C85" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -2733,7 +2650,6 @@
       <c r="F85" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2744,7 +2660,7 @@
       <c r="B86" t="n">
         <v>1</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C86" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -2760,7 +2676,6 @@
       <c r="F86" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2771,7 +2686,7 @@
       <c r="B87" t="n">
         <v>1</v>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C87" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -2787,7 +2702,6 @@
       <c r="F87" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2798,7 +2712,7 @@
       <c r="B88" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C88" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -2814,7 +2728,6 @@
       <c r="F88" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2825,7 +2738,7 @@
       <c r="B89" t="n">
         <v>1</v>
       </c>
-      <c r="C89" s="1" t="n">
+      <c r="C89" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -2841,7 +2754,6 @@
       <c r="F89" s="2" t="n">
         <v>337</v>
       </c>
-      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2852,7 +2764,7 @@
       <c r="B90" t="n">
         <v>1</v>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C90" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -2868,7 +2780,6 @@
       <c r="F90" s="2" t="n">
         <v>375</v>
       </c>
-      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2879,7 +2790,7 @@
       <c r="B91" t="n">
         <v>1</v>
       </c>
-      <c r="C91" s="1" t="n">
+      <c r="C91" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -2895,7 +2806,6 @@
       <c r="F91" s="2" t="n">
         <v>606</v>
       </c>
-      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2906,7 +2816,7 @@
       <c r="B92" t="n">
         <v>1</v>
       </c>
-      <c r="C92" s="1" t="n">
+      <c r="C92" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -2922,7 +2832,6 @@
       <c r="F92" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2933,7 +2842,7 @@
       <c r="B93" t="n">
         <v>1</v>
       </c>
-      <c r="C93" s="1" t="n">
+      <c r="C93" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -2949,7 +2858,6 @@
       <c r="F93" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2960,7 +2868,7 @@
       <c r="B94" t="n">
         <v>1</v>
       </c>
-      <c r="C94" s="1" t="n">
+      <c r="C94" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -2976,7 +2884,6 @@
       <c r="F94" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2987,7 +2894,7 @@
       <c r="B95" t="n">
         <v>1</v>
       </c>
-      <c r="C95" s="1" t="n">
+      <c r="C95" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D95" t="inlineStr">
@@ -3003,7 +2910,6 @@
       <c r="F95" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3014,7 +2920,7 @@
       <c r="B96" t="n">
         <v>1</v>
       </c>
-      <c r="C96" s="1" t="n">
+      <c r="C96" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D96" t="inlineStr">
@@ -3030,7 +2936,6 @@
       <c r="F96" s="2" t="n">
         <v>671</v>
       </c>
-      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3041,7 +2946,7 @@
       <c r="B97" t="n">
         <v>1</v>
       </c>
-      <c r="C97" s="1" t="n">
+      <c r="C97" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -3057,7 +2962,6 @@
       <c r="F97" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3068,7 +2972,7 @@
       <c r="B98" t="n">
         <v>1</v>
       </c>
-      <c r="C98" s="1" t="n">
+      <c r="C98" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -3084,7 +2988,6 @@
       <c r="F98" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3095,7 +2998,7 @@
       <c r="B99" t="n">
         <v>1</v>
       </c>
-      <c r="C99" s="1" t="n">
+      <c r="C99" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -3111,7 +3014,6 @@
       <c r="F99" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3122,7 +3024,7 @@
       <c r="B100" t="n">
         <v>1</v>
       </c>
-      <c r="C100" s="1" t="n">
+      <c r="C100" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -3138,7 +3040,6 @@
       <c r="F100" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3149,7 +3050,7 @@
       <c r="B101" t="n">
         <v>1</v>
       </c>
-      <c r="C101" s="1" t="n">
+      <c r="C101" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D101" t="inlineStr">
@@ -3165,7 +3066,6 @@
       <c r="F101" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3176,7 +3076,7 @@
       <c r="B102" t="n">
         <v>1</v>
       </c>
-      <c r="C102" s="1" t="n">
+      <c r="C102" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D102" t="inlineStr">
@@ -3192,7 +3092,6 @@
       <c r="F102" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3203,7 +3102,7 @@
       <c r="B103" t="n">
         <v>1</v>
       </c>
-      <c r="C103" s="1" t="n">
+      <c r="C103" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D103" t="inlineStr">
@@ -3219,7 +3118,6 @@
       <c r="F103" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3230,7 +3128,7 @@
       <c r="B104" t="n">
         <v>1</v>
       </c>
-      <c r="C104" s="1" t="n">
+      <c r="C104" s="3" t="n">
         <v>45545</v>
       </c>
       <c r="D104" t="inlineStr">
@@ -3246,7 +3144,6 @@
       <c r="F104" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3257,7 +3154,7 @@
       <c r="B105" t="n">
         <v>1</v>
       </c>
-      <c r="C105" s="1" t="n">
+      <c r="C105" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D105" t="inlineStr">
@@ -3273,7 +3170,6 @@
       <c r="F105" s="2" t="n">
         <v>17619</v>
       </c>
-      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3284,7 +3180,7 @@
       <c r="B106" t="n">
         <v>1</v>
       </c>
-      <c r="C106" s="1" t="n">
+      <c r="C106" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D106" t="inlineStr">
@@ -3300,7 +3196,6 @@
       <c r="F106" s="2" t="n">
         <v>16698</v>
       </c>
-      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3311,7 +3206,7 @@
       <c r="B107" t="n">
         <v>1</v>
       </c>
-      <c r="C107" s="1" t="n">
+      <c r="C107" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D107" t="inlineStr">
@@ -3327,7 +3222,6 @@
       <c r="F107" s="2" t="n">
         <v>15607</v>
       </c>
-      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3338,7 +3232,7 @@
       <c r="B108" t="n">
         <v>1</v>
       </c>
-      <c r="C108" s="1" t="n">
+      <c r="C108" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D108" t="inlineStr">
@@ -3354,7 +3248,6 @@
       <c r="F108" s="2" t="n">
         <v>16364</v>
       </c>
-      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3365,7 +3258,7 @@
       <c r="B109" t="n">
         <v>1</v>
       </c>
-      <c r="C109" s="1" t="n">
+      <c r="C109" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D109" t="inlineStr">
@@ -3381,7 +3274,6 @@
       <c r="F109" s="2" t="n">
         <v>17536</v>
       </c>
-      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3392,7 +3284,7 @@
       <c r="B110" t="n">
         <v>1</v>
       </c>
-      <c r="C110" s="1" t="n">
+      <c r="C110" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D110" t="inlineStr">
@@ -3408,7 +3300,6 @@
       <c r="F110" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3419,7 +3310,7 @@
       <c r="B111" t="n">
         <v>1</v>
       </c>
-      <c r="C111" s="1" t="n">
+      <c r="C111" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D111" t="inlineStr">
@@ -3435,7 +3326,6 @@
       <c r="F111" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3446,7 +3336,7 @@
       <c r="B112" t="n">
         <v>1</v>
       </c>
-      <c r="C112" s="1" t="n">
+      <c r="C112" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D112" t="inlineStr">
@@ -3462,7 +3352,6 @@
       <c r="F112" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3473,7 +3362,7 @@
       <c r="B113" t="n">
         <v>1</v>
       </c>
-      <c r="C113" s="1" t="n">
+      <c r="C113" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D113" t="inlineStr">
@@ -3489,7 +3378,6 @@
       <c r="F113" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3500,7 +3388,7 @@
       <c r="B114" t="n">
         <v>1</v>
       </c>
-      <c r="C114" s="1" t="n">
+      <c r="C114" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D114" t="inlineStr">
@@ -3516,7 +3404,6 @@
       <c r="F114" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3527,7 +3414,7 @@
       <c r="B115" t="n">
         <v>1</v>
       </c>
-      <c r="C115" s="1" t="n">
+      <c r="C115" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D115" t="inlineStr">
@@ -3543,7 +3430,6 @@
       <c r="F115" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3554,7 +3440,7 @@
       <c r="B116" t="n">
         <v>1</v>
       </c>
-      <c r="C116" s="1" t="n">
+      <c r="C116" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D116" t="inlineStr">
@@ -3570,7 +3456,6 @@
       <c r="F116" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3581,7 +3466,7 @@
       <c r="B117" t="n">
         <v>1</v>
       </c>
-      <c r="C117" s="1" t="n">
+      <c r="C117" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D117" t="inlineStr">
@@ -3597,7 +3482,6 @@
       <c r="F117" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3608,7 +3492,7 @@
       <c r="B118" t="n">
         <v>1</v>
       </c>
-      <c r="C118" s="1" t="n">
+      <c r="C118" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D118" t="inlineStr">
@@ -3624,7 +3508,6 @@
       <c r="F118" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3635,7 +3518,7 @@
       <c r="B119" t="n">
         <v>1</v>
       </c>
-      <c r="C119" s="1" t="n">
+      <c r="C119" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D119" t="inlineStr">
@@ -3651,7 +3534,6 @@
       <c r="F119" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3662,7 +3544,7 @@
       <c r="B120" t="n">
         <v>1</v>
       </c>
-      <c r="C120" s="1" t="n">
+      <c r="C120" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D120" t="inlineStr">
@@ -3678,7 +3560,6 @@
       <c r="F120" s="2" t="n">
         <v>4868.75</v>
       </c>
-      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3689,7 +3570,7 @@
       <c r="B121" t="n">
         <v>1</v>
       </c>
-      <c r="C121" s="1" t="n">
+      <c r="C121" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D121" t="inlineStr">
@@ -3705,7 +3586,6 @@
       <c r="F121" s="2" t="n">
         <v>5421.25</v>
       </c>
-      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3716,7 +3596,7 @@
       <c r="B122" t="n">
         <v>1</v>
       </c>
-      <c r="C122" s="1" t="n">
+      <c r="C122" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D122" t="inlineStr">
@@ -3732,7 +3612,6 @@
       <c r="F122" s="2" t="n">
         <v>4762.75</v>
       </c>
-      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3743,7 +3622,7 @@
       <c r="B123" t="n">
         <v>1</v>
       </c>
-      <c r="C123" s="1" t="n">
+      <c r="C123" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D123" t="inlineStr">
@@ -3759,7 +3638,6 @@
       <c r="F123" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3770,7 +3648,7 @@
       <c r="B124" t="n">
         <v>1</v>
       </c>
-      <c r="C124" s="1" t="n">
+      <c r="C124" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D124" t="inlineStr">
@@ -3786,7 +3664,6 @@
       <c r="F124" s="2" t="n">
         <v>4646.25</v>
       </c>
-      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3797,7 +3674,7 @@
       <c r="B125" t="n">
         <v>1</v>
       </c>
-      <c r="C125" s="1" t="n">
+      <c r="C125" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D125" t="inlineStr">
@@ -3813,7 +3690,6 @@
       <c r="F125" s="2" t="n">
         <v>5398.75</v>
       </c>
-      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3824,7 +3700,7 @@
       <c r="B126" t="n">
         <v>1</v>
       </c>
-      <c r="C126" s="1" t="n">
+      <c r="C126" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D126" t="inlineStr">
@@ -3840,7 +3716,6 @@
       <c r="F126" s="2" t="n">
         <v>5713.75</v>
       </c>
-      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3851,7 +3726,7 @@
       <c r="B127" t="n">
         <v>1</v>
       </c>
-      <c r="C127" s="1" t="n">
+      <c r="C127" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D127" t="inlineStr">
@@ -3867,7 +3742,6 @@
       <c r="F127" s="2" t="n">
         <v>-2066.75</v>
       </c>
-      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3878,7 +3752,7 @@
       <c r="B128" t="n">
         <v>1</v>
       </c>
-      <c r="C128" s="1" t="n">
+      <c r="C128" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D128" t="inlineStr">
@@ -3894,7 +3768,6 @@
       <c r="F128" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3905,7 +3778,7 @@
       <c r="B129" t="n">
         <v>1</v>
       </c>
-      <c r="C129" s="1" t="n">
+      <c r="C129" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D129" t="inlineStr">
@@ -3921,7 +3794,6 @@
       <c r="F129" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3932,7 +3804,7 @@
       <c r="B130" t="n">
         <v>1</v>
       </c>
-      <c r="C130" s="1" t="n">
+      <c r="C130" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D130" t="inlineStr">
@@ -3948,7 +3820,6 @@
       <c r="F130" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3959,7 +3830,7 @@
       <c r="B131" t="n">
         <v>1</v>
       </c>
-      <c r="C131" s="1" t="n">
+      <c r="C131" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D131" t="inlineStr">
@@ -3975,7 +3846,6 @@
       <c r="F131" s="2" t="n">
         <v>3135.25</v>
       </c>
-      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3986,7 +3856,7 @@
       <c r="B132" t="n">
         <v>1</v>
       </c>
-      <c r="C132" s="1" t="n">
+      <c r="C132" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D132" t="inlineStr">
@@ -4002,7 +3872,6 @@
       <c r="F132" s="2" t="n">
         <v>3240.25</v>
       </c>
-      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4013,7 +3882,7 @@
       <c r="B133" t="n">
         <v>1</v>
       </c>
-      <c r="C133" s="1" t="n">
+      <c r="C133" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D133" t="inlineStr">
@@ -4029,7 +3898,6 @@
       <c r="F133" s="2" t="n">
         <v>3240.25</v>
       </c>
-      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4040,7 +3908,7 @@
       <c r="B134" t="n">
         <v>1</v>
       </c>
-      <c r="C134" s="1" t="n">
+      <c r="C134" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D134" t="inlineStr">
@@ -4056,7 +3924,6 @@
       <c r="F134" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4067,7 +3934,7 @@
       <c r="B135" t="n">
         <v>1</v>
       </c>
-      <c r="C135" s="1" t="n">
+      <c r="C135" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D135" t="inlineStr">
@@ -4083,7 +3950,6 @@
       <c r="F135" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4094,7 +3960,7 @@
       <c r="B136" t="n">
         <v>1</v>
       </c>
-      <c r="C136" s="1" t="n">
+      <c r="C136" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D136" t="inlineStr">
@@ -4110,7 +3976,6 @@
       <c r="F136" s="2" t="n">
         <v>225</v>
       </c>
-      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4121,7 +3986,7 @@
       <c r="B137" t="n">
         <v>1</v>
       </c>
-      <c r="C137" s="1" t="n">
+      <c r="C137" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D137" t="inlineStr">
@@ -4137,7 +4002,6 @@
       <c r="F137" s="2" t="n">
         <v>3851.5</v>
       </c>
-      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4148,7 +4012,7 @@
       <c r="B138" t="n">
         <v>1</v>
       </c>
-      <c r="C138" s="1" t="n">
+      <c r="C138" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D138" t="inlineStr">
@@ -4164,7 +4028,6 @@
       <c r="F138" s="2" t="n">
         <v>3718.5</v>
       </c>
-      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4175,7 +4038,7 @@
       <c r="B139" t="n">
         <v>1</v>
       </c>
-      <c r="C139" s="1" t="n">
+      <c r="C139" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D139" t="inlineStr">
@@ -4191,7 +4054,6 @@
       <c r="F139" s="2" t="n">
         <v>3718.5</v>
       </c>
-      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4202,7 +4064,7 @@
       <c r="B140" t="n">
         <v>1</v>
       </c>
-      <c r="C140" s="1" t="n">
+      <c r="C140" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D140" t="inlineStr">
@@ -4218,7 +4080,6 @@
       <c r="F140" s="2" t="n">
         <v>2995.75</v>
       </c>
-      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4229,7 +4090,7 @@
       <c r="B141" t="n">
         <v>1</v>
       </c>
-      <c r="C141" s="1" t="n">
+      <c r="C141" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D141" t="inlineStr">
@@ -4245,7 +4106,6 @@
       <c r="F141" s="2" t="n">
         <v>3901.75</v>
       </c>
-      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4256,7 +4116,7 @@
       <c r="B142" t="n">
         <v>1</v>
       </c>
-      <c r="C142" s="1" t="n">
+      <c r="C142" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D142" t="inlineStr">
@@ -4272,7 +4132,6 @@
       <c r="F142" s="2" t="n">
         <v>3593.75</v>
       </c>
-      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4283,7 +4142,7 @@
       <c r="B143" t="n">
         <v>1</v>
       </c>
-      <c r="C143" s="1" t="n">
+      <c r="C143" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D143" t="inlineStr">
@@ -4299,7 +4158,6 @@
       <c r="F143" s="2" t="n">
         <v>3962</v>
       </c>
-      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4310,7 +4168,7 @@
       <c r="B144" t="n">
         <v>1</v>
       </c>
-      <c r="C144" s="1" t="n">
+      <c r="C144" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D144" t="inlineStr">
@@ -4326,7 +4184,6 @@
       <c r="F144" s="2" t="n">
         <v>3894.25</v>
       </c>
-      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4337,7 +4194,7 @@
       <c r="B145" t="n">
         <v>1</v>
       </c>
-      <c r="C145" s="1" t="n">
+      <c r="C145" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D145" t="inlineStr">
@@ -4353,7 +4210,6 @@
       <c r="F145" s="2" t="n">
         <v>3908.5</v>
       </c>
-      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4364,7 +4220,7 @@
       <c r="B146" t="n">
         <v>1</v>
       </c>
-      <c r="C146" s="1" t="n">
+      <c r="C146" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D146" t="inlineStr">
@@ -4380,7 +4236,6 @@
       <c r="F146" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4391,7 +4246,7 @@
       <c r="B147" t="n">
         <v>1</v>
       </c>
-      <c r="C147" s="1" t="n">
+      <c r="C147" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D147" t="inlineStr">
@@ -4407,7 +4262,6 @@
       <c r="F147" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4418,7 +4272,7 @@
       <c r="B148" t="n">
         <v>1</v>
       </c>
-      <c r="C148" s="1" t="n">
+      <c r="C148" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D148" t="inlineStr">
@@ -4434,7 +4288,6 @@
       <c r="F148" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4445,7 +4298,7 @@
       <c r="B149" t="n">
         <v>1</v>
       </c>
-      <c r="C149" s="1" t="n">
+      <c r="C149" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D149" t="inlineStr">
@@ -4461,7 +4314,6 @@
       <c r="F149" s="2" t="n">
         <v>5036.75</v>
       </c>
-      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4472,7 +4324,7 @@
       <c r="B150" t="n">
         <v>1</v>
       </c>
-      <c r="C150" s="1" t="n">
+      <c r="C150" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D150" t="inlineStr">
@@ -4488,7 +4340,6 @@
       <c r="F150" s="2" t="n">
         <v>5328.75</v>
       </c>
-      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4499,7 +4350,7 @@
       <c r="B151" t="n">
         <v>1</v>
       </c>
-      <c r="C151" s="1" t="n">
+      <c r="C151" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D151" t="inlineStr">
@@ -4515,7 +4366,6 @@
       <c r="F151" s="2" t="n">
         <v>5533.75</v>
       </c>
-      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4526,7 +4376,7 @@
       <c r="B152" t="n">
         <v>1</v>
       </c>
-      <c r="C152" s="1" t="n">
+      <c r="C152" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D152" t="inlineStr">
@@ -4542,7 +4392,6 @@
       <c r="F152" s="2" t="n">
         <v>-204</v>
       </c>
-      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4553,7 +4402,7 @@
       <c r="B153" t="n">
         <v>1</v>
       </c>
-      <c r="C153" s="1" t="n">
+      <c r="C153" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D153" t="inlineStr">
@@ -4569,7 +4418,6 @@
       <c r="F153" s="2" t="n">
         <v>1474</v>
       </c>
-      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4580,7 +4428,7 @@
       <c r="B154" t="n">
         <v>1</v>
       </c>
-      <c r="C154" s="1" t="n">
+      <c r="C154" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D154" t="inlineStr">
@@ -4596,7 +4444,6 @@
       <c r="F154" s="2" t="n">
         <v>-204</v>
       </c>
-      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4607,7 +4454,7 @@
       <c r="B155" t="n">
         <v>1</v>
       </c>
-      <c r="C155" s="1" t="n">
+      <c r="C155" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D155" t="inlineStr">
@@ -4623,7 +4470,6 @@
       <c r="F155" s="2" t="n">
         <v>1213</v>
       </c>
-      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4634,7 +4480,7 @@
       <c r="B156" t="n">
         <v>1</v>
       </c>
-      <c r="C156" s="1" t="n">
+      <c r="C156" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D156" t="inlineStr">
@@ -4650,7 +4496,6 @@
       <c r="F156" s="2" t="n">
         <v>5561.5</v>
       </c>
-      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4661,7 +4506,7 @@
       <c r="B157" t="n">
         <v>1</v>
       </c>
-      <c r="C157" s="1" t="n">
+      <c r="C157" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D157" t="inlineStr">
@@ -4677,7 +4522,6 @@
       <c r="F157" s="2" t="n">
         <v>5759.25</v>
       </c>
-      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4688,7 +4532,7 @@
       <c r="B158" t="n">
         <v>1</v>
       </c>
-      <c r="C158" s="1" t="n">
+      <c r="C158" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D158" t="inlineStr">
@@ -4704,7 +4548,6 @@
       <c r="F158" s="2" t="n">
         <v>4091.5</v>
       </c>
-      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4715,7 +4558,7 @@
       <c r="B159" t="n">
         <v>1</v>
       </c>
-      <c r="C159" s="1" t="n">
+      <c r="C159" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D159" t="inlineStr">
@@ -4731,7 +4574,6 @@
       <c r="F159" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4742,7 +4584,7 @@
       <c r="B160" t="n">
         <v>1</v>
       </c>
-      <c r="C160" s="1" t="n">
+      <c r="C160" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D160" t="inlineStr">
@@ -4758,7 +4600,6 @@
       <c r="F160" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4769,7 +4610,7 @@
       <c r="B161" t="n">
         <v>1</v>
       </c>
-      <c r="C161" s="1" t="n">
+      <c r="C161" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D161" t="inlineStr">
@@ -4785,7 +4626,6 @@
       <c r="F161" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4796,7 +4636,7 @@
       <c r="B162" t="n">
         <v>1</v>
       </c>
-      <c r="C162" s="1" t="n">
+      <c r="C162" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D162" t="inlineStr">
@@ -4812,7 +4652,6 @@
       <c r="F162" s="2" t="n">
         <v>49.5</v>
       </c>
-      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4823,7 +4662,7 @@
       <c r="B163" t="n">
         <v>1</v>
       </c>
-      <c r="C163" s="1" t="n">
+      <c r="C163" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D163" t="inlineStr">
@@ -4839,7 +4678,6 @@
       <c r="F163" s="2" t="n">
         <v>-444.25</v>
       </c>
-      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4850,7 +4688,7 @@
       <c r="B164" t="n">
         <v>1</v>
       </c>
-      <c r="C164" s="1" t="n">
+      <c r="C164" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="D164" t="inlineStr">
@@ -4866,7 +4704,6 @@
       <c r="F164" s="2" t="n">
         <v>946</v>
       </c>
-      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4877,7 +4714,7 @@
       <c r="B165" t="n">
         <v>1</v>
       </c>
-      <c r="C165" s="1" t="n">
+      <c r="C165" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D165" t="inlineStr">
@@ -4893,7 +4730,6 @@
       <c r="F165" s="2" t="n">
         <v>4983.85</v>
       </c>
-      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4904,7 +4740,7 @@
       <c r="B166" t="n">
         <v>1</v>
       </c>
-      <c r="C166" s="1" t="n">
+      <c r="C166" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D166" t="inlineStr">
@@ -4920,7 +4756,6 @@
       <c r="F166" s="2" t="n">
         <v>4983.85</v>
       </c>
-      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4931,7 +4766,7 @@
       <c r="B167" t="n">
         <v>1</v>
       </c>
-      <c r="C167" s="1" t="n">
+      <c r="C167" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D167" t="inlineStr">
@@ -4947,7 +4782,6 @@
       <c r="F167" s="2" t="n">
         <v>4983.85</v>
       </c>
-      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4958,7 +4792,7 @@
       <c r="B168" t="n">
         <v>1</v>
       </c>
-      <c r="C168" s="1" t="n">
+      <c r="C168" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D168" t="inlineStr">
@@ -4974,7 +4808,6 @@
       <c r="F168" s="2" t="n">
         <v>965</v>
       </c>
-      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4985,7 +4818,7 @@
       <c r="B169" t="n">
         <v>1</v>
       </c>
-      <c r="C169" s="1" t="n">
+      <c r="C169" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D169" t="inlineStr">
@@ -5001,7 +4834,6 @@
       <c r="F169" s="2" t="n">
         <v>965</v>
       </c>
-      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5012,7 +4844,7 @@
       <c r="B170" t="n">
         <v>1</v>
       </c>
-      <c r="C170" s="1" t="n">
+      <c r="C170" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D170" t="inlineStr">
@@ -5028,7 +4860,6 @@
       <c r="F170" s="2" t="n">
         <v>965</v>
       </c>
-      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5039,7 +4870,7 @@
       <c r="B171" t="n">
         <v>1</v>
       </c>
-      <c r="C171" s="1" t="n">
+      <c r="C171" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D171" t="inlineStr">
@@ -5055,7 +4886,6 @@
       <c r="F171" s="2" t="n">
         <v>5661.53</v>
       </c>
-      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5066,7 +4896,7 @@
       <c r="B172" t="n">
         <v>1</v>
       </c>
-      <c r="C172" s="1" t="n">
+      <c r="C172" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D172" t="inlineStr">
@@ -5082,7 +4912,6 @@
       <c r="F172" s="2" t="n">
         <v>5661.53</v>
       </c>
-      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5093,7 +4922,7 @@
       <c r="B173" t="n">
         <v>1</v>
       </c>
-      <c r="C173" s="1" t="n">
+      <c r="C173" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D173" t="inlineStr">
@@ -5109,7 +4938,6 @@
       <c r="F173" s="2" t="n">
         <v>5661.53</v>
       </c>
-      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5120,7 +4948,7 @@
       <c r="B174" t="n">
         <v>1</v>
       </c>
-      <c r="C174" s="1" t="n">
+      <c r="C174" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D174" t="inlineStr">
@@ -5136,7 +4964,6 @@
       <c r="F174" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5147,7 +4974,7 @@
       <c r="B175" t="n">
         <v>1</v>
       </c>
-      <c r="C175" s="1" t="n">
+      <c r="C175" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D175" t="inlineStr">
@@ -5163,7 +4990,6 @@
       <c r="F175" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5174,7 +5000,7 @@
       <c r="B176" t="n">
         <v>1</v>
       </c>
-      <c r="C176" s="1" t="n">
+      <c r="C176" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D176" t="inlineStr">
@@ -5190,7 +5016,6 @@
       <c r="F176" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5201,7 +5026,7 @@
       <c r="B177" t="n">
         <v>1</v>
       </c>
-      <c r="C177" s="1" t="n">
+      <c r="C177" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D177" t="inlineStr">
@@ -5217,7 +5042,6 @@
       <c r="F177" s="2" t="n">
         <v>4458.74</v>
       </c>
-      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5228,7 +5052,7 @@
       <c r="B178" t="n">
         <v>1</v>
       </c>
-      <c r="C178" s="1" t="n">
+      <c r="C178" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D178" t="inlineStr">
@@ -5244,7 +5068,6 @@
       <c r="F178" s="2" t="n">
         <v>4769.37</v>
       </c>
-      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5255,7 +5078,7 @@
       <c r="B179" t="n">
         <v>1</v>
       </c>
-      <c r="C179" s="1" t="n">
+      <c r="C179" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D179" t="inlineStr">
@@ -5271,7 +5094,6 @@
       <c r="F179" s="2" t="n">
         <v>4673.79</v>
       </c>
-      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5282,7 +5104,7 @@
       <c r="B180" t="n">
         <v>1</v>
       </c>
-      <c r="C180" s="1" t="n">
+      <c r="C180" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D180" t="inlineStr">
@@ -5298,7 +5120,6 @@
       <c r="F180" s="2" t="n">
         <v>-71.69</v>
       </c>
-      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5309,7 +5130,7 @@
       <c r="B181" t="n">
         <v>1</v>
       </c>
-      <c r="C181" s="1" t="n">
+      <c r="C181" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D181" t="inlineStr">
@@ -5325,7 +5146,6 @@
       <c r="F181" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5336,7 +5156,7 @@
       <c r="B182" t="n">
         <v>1</v>
       </c>
-      <c r="C182" s="1" t="n">
+      <c r="C182" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D182" t="inlineStr">
@@ -5352,7 +5172,6 @@
       <c r="F182" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5363,7 +5182,7 @@
       <c r="B183" t="n">
         <v>1</v>
       </c>
-      <c r="C183" s="1" t="n">
+      <c r="C183" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D183" t="inlineStr">
@@ -5379,7 +5198,6 @@
       <c r="F183" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5390,7 +5208,7 @@
       <c r="B184" t="n">
         <v>1</v>
       </c>
-      <c r="C184" s="1" t="n">
+      <c r="C184" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D184" t="inlineStr">
@@ -5406,7 +5224,6 @@
       <c r="F184" s="2" t="n">
         <v>4856.21</v>
       </c>
-      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5417,7 +5234,7 @@
       <c r="B185" t="n">
         <v>1</v>
       </c>
-      <c r="C185" s="1" t="n">
+      <c r="C185" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D185" t="inlineStr">
@@ -5433,7 +5250,6 @@
       <c r="F185" s="2" t="n">
         <v>4832.31</v>
       </c>
-      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5444,7 +5260,7 @@
       <c r="B186" t="n">
         <v>1</v>
       </c>
-      <c r="C186" s="1" t="n">
+      <c r="C186" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D186" t="inlineStr">
@@ -5460,7 +5276,6 @@
       <c r="F186" s="2" t="n">
         <v>4426.11</v>
       </c>
-      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5471,7 +5286,7 @@
       <c r="B187" t="n">
         <v>1</v>
       </c>
-      <c r="C187" s="1" t="n">
+      <c r="C187" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D187" t="inlineStr">
@@ -5487,7 +5302,6 @@
       <c r="F187" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5498,7 +5312,7 @@
       <c r="B188" t="n">
         <v>1</v>
       </c>
-      <c r="C188" s="1" t="n">
+      <c r="C188" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D188" t="inlineStr">
@@ -5514,7 +5328,6 @@
       <c r="F188" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5525,7 +5338,7 @@
       <c r="B189" t="n">
         <v>1</v>
       </c>
-      <c r="C189" s="1" t="n">
+      <c r="C189" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D189" t="inlineStr">
@@ -5541,7 +5354,6 @@
       <c r="F189" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5552,7 +5364,7 @@
       <c r="B190" t="n">
         <v>1</v>
       </c>
-      <c r="C190" s="1" t="n">
+      <c r="C190" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D190" t="inlineStr">
@@ -5568,7 +5380,6 @@
       <c r="F190" s="2" t="n">
         <v>3053.74</v>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5579,7 +5390,7 @@
       <c r="B191" t="n">
         <v>1</v>
       </c>
-      <c r="C191" s="1" t="n">
+      <c r="C191" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D191" t="inlineStr">
@@ -5595,7 +5406,6 @@
       <c r="F191" s="2" t="n">
         <v>3149.31</v>
       </c>
-      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5606,7 +5416,7 @@
       <c r="B192" t="n">
         <v>1</v>
       </c>
-      <c r="C192" s="1" t="n">
+      <c r="C192" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D192" t="inlineStr">
@@ -5622,7 +5432,6 @@
       <c r="F192" s="2" t="n">
         <v>4907.96</v>
       </c>
-      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5633,7 +5442,7 @@
       <c r="B193" t="n">
         <v>1</v>
       </c>
-      <c r="C193" s="1" t="n">
+      <c r="C193" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D193" t="inlineStr">
@@ -5649,7 +5458,6 @@
       <c r="F193" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5660,7 +5468,7 @@
       <c r="B194" t="n">
         <v>1</v>
       </c>
-      <c r="C194" s="1" t="n">
+      <c r="C194" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D194" t="inlineStr">
@@ -5676,7 +5484,6 @@
       <c r="F194" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5687,7 +5494,7 @@
       <c r="B195" t="n">
         <v>1</v>
       </c>
-      <c r="C195" s="1" t="n">
+      <c r="C195" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D195" t="inlineStr">
@@ -5703,7 +5510,6 @@
       <c r="F195" s="2" t="n">
         <v>49.88</v>
       </c>
-      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5714,7 +5520,7 @@
       <c r="B196" t="n">
         <v>1</v>
       </c>
-      <c r="C196" s="1" t="n">
+      <c r="C196" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D196" t="inlineStr">
@@ -5730,7 +5536,6 @@
       <c r="F196" s="2" t="n">
         <v>4688.35</v>
       </c>
-      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5741,7 +5546,7 @@
       <c r="B197" t="n">
         <v>1</v>
       </c>
-      <c r="C197" s="1" t="n">
+      <c r="C197" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D197" t="inlineStr">
@@ -5757,7 +5562,6 @@
       <c r="F197" s="2" t="n">
         <v>4688.35</v>
       </c>
-      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5768,7 +5572,7 @@
       <c r="B198" t="n">
         <v>1</v>
       </c>
-      <c r="C198" s="1" t="n">
+      <c r="C198" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D198" t="inlineStr">
@@ -5784,7 +5588,6 @@
       <c r="F198" s="2" t="n">
         <v>4688.35</v>
       </c>
-      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5795,7 +5598,7 @@
       <c r="B199" t="n">
         <v>1</v>
       </c>
-      <c r="C199" s="1" t="n">
+      <c r="C199" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D199" t="inlineStr">
@@ -5811,7 +5614,6 @@
       <c r="F199" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5822,7 +5624,7 @@
       <c r="B200" t="n">
         <v>1</v>
       </c>
-      <c r="C200" s="1" t="n">
+      <c r="C200" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D200" t="inlineStr">
@@ -5838,7 +5640,6 @@
       <c r="F200" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5849,7 +5650,7 @@
       <c r="B201" t="n">
         <v>1</v>
       </c>
-      <c r="C201" s="1" t="n">
+      <c r="C201" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="D201" t="inlineStr">
@@ -5865,7 +5666,6 @@
       <c r="F201" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5876,7 +5676,7 @@
       <c r="B202" t="n">
         <v>1</v>
       </c>
-      <c r="C202" s="1" t="n">
+      <c r="C202" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
@@ -5892,7 +5692,6 @@
       <c r="F202" s="2" t="n">
         <v>4800</v>
       </c>
-      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5903,7 +5702,7 @@
       <c r="B203" t="n">
         <v>1</v>
       </c>
-      <c r="C203" s="1" t="n">
+      <c r="C203" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
@@ -5919,7 +5718,6 @@
       <c r="F203" s="2" t="n">
         <v>4800</v>
       </c>
-      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5930,7 +5728,7 @@
       <c r="B204" t="n">
         <v>1</v>
       </c>
-      <c r="C204" s="1" t="n">
+      <c r="C204" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
@@ -5946,7 +5744,6 @@
       <c r="F204" s="2" t="n">
         <v>4800</v>
       </c>
-      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5957,7 +5754,7 @@
       <c r="B205" t="n">
         <v>1</v>
       </c>
-      <c r="C205" s="1" t="n">
+      <c r="C205" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
@@ -5973,7 +5770,6 @@
       <c r="F205" s="2" t="n">
         <v>4800</v>
       </c>
-      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5984,7 +5780,7 @@
       <c r="B206" t="n">
         <v>1</v>
       </c>
-      <c r="C206" s="1" t="n">
+      <c r="C206" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D206" t="inlineStr">
@@ -6000,7 +5796,6 @@
       <c r="F206" s="2" t="n">
         <v>13591.5</v>
       </c>
-      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6011,7 +5806,7 @@
       <c r="B207" t="n">
         <v>1</v>
       </c>
-      <c r="C207" s="1" t="n">
+      <c r="C207" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D207" t="inlineStr">
@@ -6027,7 +5822,6 @@
       <c r="F207" s="2" t="n">
         <v>14497.6</v>
       </c>
-      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6038,7 +5832,7 @@
       <c r="B208" t="n">
         <v>1</v>
       </c>
-      <c r="C208" s="1" t="n">
+      <c r="C208" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="D208" t="inlineStr">
@@ -6054,7 +5848,6 @@
       <c r="F208" s="2" t="n">
         <v>17215.9</v>
       </c>
-      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6065,7 +5858,7 @@
       <c r="B209" t="n">
         <v>1</v>
       </c>
-      <c r="C209" s="1" t="n">
+      <c r="C209" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D209" t="inlineStr">
@@ -6096,7 +5889,7 @@
       <c r="B210" t="n">
         <v>1</v>
       </c>
-      <c r="C210" s="1" t="n">
+      <c r="C210" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D210" t="inlineStr">
@@ -6127,7 +5920,7 @@
       <c r="B211" t="n">
         <v>1</v>
       </c>
-      <c r="C211" s="1" t="n">
+      <c r="C211" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D211" t="inlineStr">
@@ -6158,7 +5951,7 @@
       <c r="B212" t="n">
         <v>1</v>
       </c>
-      <c r="C212" s="1" t="n">
+      <c r="C212" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D212" t="inlineStr">
@@ -6189,7 +5982,7 @@
       <c r="B213" t="n">
         <v>1</v>
       </c>
-      <c r="C213" s="1" t="n">
+      <c r="C213" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D213" t="inlineStr">
@@ -6220,7 +6013,7 @@
       <c r="B214" t="n">
         <v>1</v>
       </c>
-      <c r="C214" s="1" t="n">
+      <c r="C214" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D214" t="inlineStr">
@@ -6251,7 +6044,7 @@
       <c r="B215" t="n">
         <v>1</v>
       </c>
-      <c r="C215" s="1" t="n">
+      <c r="C215" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D215" t="inlineStr">
@@ -6282,7 +6075,7 @@
       <c r="B216" t="n">
         <v>1</v>
       </c>
-      <c r="C216" s="1" t="n">
+      <c r="C216" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D216" t="inlineStr">
@@ -6313,7 +6106,7 @@
       <c r="B217" t="n">
         <v>1</v>
       </c>
-      <c r="C217" s="1" t="n">
+      <c r="C217" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D217" t="inlineStr">
@@ -6344,7 +6137,7 @@
       <c r="B218" t="n">
         <v>1</v>
       </c>
-      <c r="C218" s="1" t="n">
+      <c r="C218" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D218" t="inlineStr">
@@ -6375,7 +6168,7 @@
       <c r="B219" t="n">
         <v>1</v>
       </c>
-      <c r="C219" s="1" t="n">
+      <c r="C219" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D219" t="inlineStr">
@@ -6406,7 +6199,7 @@
       <c r="B220" t="n">
         <v>1</v>
       </c>
-      <c r="C220" s="1" t="n">
+      <c r="C220" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D220" t="inlineStr">
@@ -6437,7 +6230,7 @@
       <c r="B221" t="n">
         <v>1</v>
       </c>
-      <c r="C221" s="1" t="n">
+      <c r="C221" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D221" t="inlineStr">
@@ -6468,7 +6261,7 @@
       <c r="B222" t="n">
         <v>1</v>
       </c>
-      <c r="C222" s="1" t="n">
+      <c r="C222" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D222" t="inlineStr">
@@ -6499,7 +6292,7 @@
       <c r="B223" t="n">
         <v>1</v>
       </c>
-      <c r="C223" s="1" t="n">
+      <c r="C223" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D223" t="inlineStr">
@@ -6530,7 +6323,7 @@
       <c r="B224" t="n">
         <v>1</v>
       </c>
-      <c r="C224" s="1" t="n">
+      <c r="C224" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D224" t="inlineStr">
@@ -6561,7 +6354,7 @@
       <c r="B225" t="n">
         <v>1</v>
       </c>
-      <c r="C225" s="1" t="n">
+      <c r="C225" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D225" t="inlineStr">
@@ -6592,7 +6385,7 @@
       <c r="B226" t="n">
         <v>1</v>
       </c>
-      <c r="C226" s="1" t="n">
+      <c r="C226" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D226" t="inlineStr">
@@ -6623,7 +6416,7 @@
       <c r="B227" t="n">
         <v>1</v>
       </c>
-      <c r="C227" s="1" t="n">
+      <c r="C227" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D227" t="inlineStr">
@@ -6654,7 +6447,7 @@
       <c r="B228" t="n">
         <v>1</v>
       </c>
-      <c r="C228" s="1" t="n">
+      <c r="C228" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D228" t="inlineStr">
@@ -6685,7 +6478,7 @@
       <c r="B229" t="n">
         <v>1</v>
       </c>
-      <c r="C229" s="1" t="n">
+      <c r="C229" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D229" t="inlineStr">
@@ -6716,7 +6509,7 @@
       <c r="B230" t="n">
         <v>1</v>
       </c>
-      <c r="C230" s="1" t="n">
+      <c r="C230" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D230" t="inlineStr">
@@ -6747,7 +6540,7 @@
       <c r="B231" t="n">
         <v>1</v>
       </c>
-      <c r="C231" s="1" t="n">
+      <c r="C231" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D231" t="inlineStr">
@@ -6778,7 +6571,7 @@
       <c r="B232" t="n">
         <v>1</v>
       </c>
-      <c r="C232" s="1" t="n">
+      <c r="C232" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D232" t="inlineStr">
@@ -6809,7 +6602,7 @@
       <c r="B233" t="n">
         <v>1</v>
       </c>
-      <c r="C233" s="1" t="n">
+      <c r="C233" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D233" t="inlineStr">
@@ -6840,7 +6633,7 @@
       <c r="B234" t="n">
         <v>1</v>
       </c>
-      <c r="C234" s="1" t="n">
+      <c r="C234" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D234" t="inlineStr">
@@ -6871,7 +6664,7 @@
       <c r="B235" t="n">
         <v>1</v>
       </c>
-      <c r="C235" s="1" t="n">
+      <c r="C235" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D235" t="inlineStr">
@@ -6902,7 +6695,7 @@
       <c r="B236" t="n">
         <v>1</v>
       </c>
-      <c r="C236" s="1" t="n">
+      <c r="C236" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D236" t="inlineStr">
@@ -6933,7 +6726,7 @@
       <c r="B237" t="n">
         <v>1</v>
       </c>
-      <c r="C237" s="1" t="n">
+      <c r="C237" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D237" t="inlineStr">
@@ -6964,7 +6757,7 @@
       <c r="B238" t="n">
         <v>1</v>
       </c>
-      <c r="C238" s="1" t="n">
+      <c r="C238" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D238" t="inlineStr">
@@ -6995,7 +6788,7 @@
       <c r="B239" t="n">
         <v>1</v>
       </c>
-      <c r="C239" s="1" t="n">
+      <c r="C239" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D239" t="inlineStr">
@@ -7026,7 +6819,7 @@
       <c r="B240" t="n">
         <v>1</v>
       </c>
-      <c r="C240" s="1" t="n">
+      <c r="C240" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D240" t="inlineStr">
@@ -7057,7 +6850,7 @@
       <c r="B241" t="n">
         <v>1</v>
       </c>
-      <c r="C241" s="1" t="n">
+      <c r="C241" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D241" t="inlineStr">
@@ -7088,7 +6881,7 @@
       <c r="B242" t="n">
         <v>1</v>
       </c>
-      <c r="C242" s="1" t="n">
+      <c r="C242" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D242" t="inlineStr">
@@ -7119,7 +6912,7 @@
       <c r="B243" t="n">
         <v>1</v>
       </c>
-      <c r="C243" s="1" t="n">
+      <c r="C243" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D243" t="inlineStr">
@@ -7150,7 +6943,7 @@
       <c r="B244" t="n">
         <v>1</v>
       </c>
-      <c r="C244" s="1" t="n">
+      <c r="C244" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D244" t="inlineStr">
@@ -7181,7 +6974,7 @@
       <c r="B245" t="n">
         <v>1</v>
       </c>
-      <c r="C245" s="1" t="n">
+      <c r="C245" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D245" t="inlineStr">
@@ -7212,7 +7005,7 @@
       <c r="B246" t="n">
         <v>1</v>
       </c>
-      <c r="C246" s="1" t="n">
+      <c r="C246" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D246" t="inlineStr">
@@ -7243,7 +7036,7 @@
       <c r="B247" t="n">
         <v>1</v>
       </c>
-      <c r="C247" s="1" t="n">
+      <c r="C247" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D247" t="inlineStr">
@@ -7274,7 +7067,7 @@
       <c r="B248" t="n">
         <v>1</v>
       </c>
-      <c r="C248" s="1" t="n">
+      <c r="C248" s="3" t="n">
         <v>45995</v>
       </c>
       <c r="D248" t="inlineStr">
@@ -7305,7 +7098,7 @@
       <c r="B249" t="n">
         <v>1</v>
       </c>
-      <c r="C249" s="1" t="n">
+      <c r="C249" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="D249" t="inlineStr">
@@ -7336,7 +7129,7 @@
       <c r="B250" t="n">
         <v>1</v>
       </c>
-      <c r="C250" s="1" t="n">
+      <c r="C250" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="D250" t="inlineStr">
@@ -7367,7 +7160,7 @@
       <c r="B251" t="n">
         <v>1</v>
       </c>
-      <c r="C251" s="1" t="n">
+      <c r="C251" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="D251" t="inlineStr">
@@ -7398,7 +7191,7 @@
       <c r="B252" t="n">
         <v>1</v>
       </c>
-      <c r="C252" s="1" t="n">
+      <c r="C252" s="3" t="n">
         <v>46098</v>
       </c>
       <c r="D252" t="inlineStr">
@@ -7429,7 +7222,7 @@
       <c r="B253" t="n">
         <v>1</v>
       </c>
-      <c r="C253" s="1" t="n">
+      <c r="C253" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D253" t="inlineStr">
@@ -7460,7 +7253,7 @@
       <c r="B254" t="n">
         <v>1</v>
       </c>
-      <c r="C254" s="1" t="n">
+      <c r="C254" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D254" t="inlineStr">
@@ -7491,7 +7284,7 @@
       <c r="B255" t="n">
         <v>1</v>
       </c>
-      <c r="C255" s="1" t="n">
+      <c r="C255" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="D255" t="inlineStr">
@@ -7510,6 +7303,2176 @@
       <c r="G255" t="inlineStr">
         <is>
           <t>Price reduced from contract approved by Tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="n">
+        <v>25737</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="n">
+        <v>26197</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>50-3</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="n">
+        <v>28444</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>50-3</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="n">
+        <v>1058</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>50-3</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDDNR12</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>50-3</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDKIT12</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>50-1</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>FND-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>50-2</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>FND-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="n">
+        <v>453</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="n">
+        <v>30334</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>60-2</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="n">
+        <v>30873</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>60-3</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="n">
+        <v>30559</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>60-4</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="n">
+        <v>32641</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>60-2</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>60-2</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>60-4</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMC</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1</v>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>60-4</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>FND-OC1ESEDMUL01</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>60-4</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDCYD12</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="n">
+        <v>671</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDDNR12</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>60-2</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>60-3</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>60-4</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>FND-OC1ESGDGTH12</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>60-1</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>FND-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Ashland - Concrete</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>60-2</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>FND-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>1</v>
+      </c>
+      <c r="C290" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>60-1 - Liberty</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Flatwork</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>4745.25</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>1</v>
+      </c>
+      <c r="C291" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>60-2 - Patriot</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Flatwork</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>5981</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>60-3 - Pioneer</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Flatwork</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>5723.75</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Flatwork</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="n">
+        <v>6027.75</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>1</v>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>FW-FW2CYDA01</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="n">
+        <v>-1116.25</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>FW-FW2CYDA02</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="n">
+        <v>749.99</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>60-3 - Pioneer</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>FW-MODL0000FW</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="n">
+        <v>4361.25</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>FW-MODL0000FW</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="n">
+        <v>2846</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>60-1 - Liberty</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>FW-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>1</v>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>60-3 - Pioneer</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>FW-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>FW-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>60-2 - Patriot</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>FW-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>60-2 - Patriot</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>FW-OC1ESDRGAR01</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>60-4 - Summit</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>FW-OC1ESGDCYD12</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>60-1 - Liberty</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>FW-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Ashland 60 Flatwork - Concrete</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" s="3" t="n">
+        <v>45870</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>60-2 - Patriot</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>FW-OC1ODLA01</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="n">
+        <v>770</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>TM addendum eff 8/1/25 (signed 10/3/25): price reduction due to drain removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>E302B2294 - Plan 1 - Redwood</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="n">
+        <v>18578</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>E302B2758 - Plan 5 - Willow</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="n">
+        <v>18256</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>E302C2448 - Plan 2 - Sycamore</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="n">
+        <v>17867</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>E302C2507 - Plan 3 - Teak</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="n">
+        <v>16256</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>E302C2597 - Plan 4 - Willow</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="n">
+        <v>17442</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>E302B2294 - Plan 1 - Redwood</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>FND-OC1BALA04</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="n">
+        <v>2296</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>E302B2758 - Plan 5 - Willow</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>FND-OC1BALA04</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="n">
+        <v>2206</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>E302C2448 - Plan 2 - Sycamore</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>FND-OC1BALA04</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="n">
+        <v>2127</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>E302C2507 - Plan 3 - Teak</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>FND-OC1BALA04</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="n">
+        <v>1362</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>1</v>
+      </c>
+      <c r="C315" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>E302C2597 - Plan 4 - Willow</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>FND-OC1BALA04</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="n">
+        <v>1664</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>E302C2448 - Plan 2 - Sycamore</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>FND-OC1ELVMB</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="n">
+        <v>489</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>E302B2294 - Plan 1 - Redwood</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>FND-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>E302B2758 - Plan 5 - Willow</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>FND-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>E302C2448 - Plan 2 - Sycamore</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>FND-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>E302C2507 - Plan 3 - Teak</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>FND-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Opus at Cadence 30s - Concrete</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" s="3" t="n">
+        <v>45901</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>E302C2597 - Plan 4 - Willow</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>FND-OC1ESDRGAR</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>TM addendum eff 9/1/25 (signed 9/21/25): price reduction for opting out of OCIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>MF Ovation 45s</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Plan 1</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>TM addendum eff 4/1/24 (re-issued 11/4/25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>MF Ovation 45s</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Plan 4</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>TM addendum eff 4/1/24 (re-issued 11/4/25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>MF Ovation 45s</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Plan 1</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additional…</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>TM addendum eff 4/1/24 (re-issued 11/4/25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>MF Ovation 45s</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" s="3" t="n">
+        <v>45383</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Plan 4</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>LSO-WHITESHEET01 White Sheet "Site Conditions" - Additional…</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>TM addendum eff 4/1/24 (re-issued 11/4/25)</t>
         </is>
       </c>
     </row>
